--- a/虚拟棋战_棋子与羁绊_20260914.xlsx
+++ b/虚拟棋战_棋子与羁绊_20260914.xlsx
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>近战·物理·射程1·攻速1.2·卡池20张</t>
+          <t>远程·物理·射程3·攻速1.2·卡池20张</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">

--- a/虚拟棋战_棋子与羁绊_20260914.xlsx
+++ b/虚拟棋战_棋子与羁绊_20260914.xlsx
@@ -1752,7 +1752,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>咩栗</t>
+          <t>真绯瑠</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>栗刺旋风：对周围 1 格内所有敌人造成 189% 攻击伤害，并将其击退 1 格</t>
+          <t>绯红旋风：对周围 1 格内所有敌人造成 189% 攻击伤害，并将其击退 1 格</t>
         </is>
       </c>
     </row>
@@ -2049,9 +2049,9 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2人：刀客护甲 +8
-4人：刀客护甲 +12
-6人：刀客护甲 +16（现有成员 9 人）</t>
+          <t>2人：刀客护甲 +7
+4人：刀客护甲 +11
+6人：刀客护甲 +14（现有成员 9 人）</t>
         </is>
       </c>
     </row>
@@ -2105,8 +2105,8 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>3人：游侠攻击 20% 概率弹射至最近的另一名敌人，造成 60% 攻击伤害
-4人：弹射概率提升至 35%（现有成员 4 人）</t>
+          <t>3人：游侠攻击 25% 概率弹射至最近的另一名敌人，造成 70% 攻击伤害
+4人：弹射概率提升至 40%（现有成员 4 人）</t>
         </is>
       </c>
     </row>
@@ -2123,8 +2123,8 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>3人：敌方全体魔法抗性 -40%
-6人：敌方全体魔法抗性 -100%（现有成员 7 人）</t>
+          <t>3人：敌方全体魔法抗性 -28%
+6人：敌方全体魔法抗性 -72%（现有成员 7 人）</t>
         </is>
       </c>
     </row>
@@ -2158,8 +2158,8 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>3人：刺客攻击 15% 概率造成 3 倍暴击
-6人：暴击伤害提升至 4 倍（现有成员 7 人）</t>
+          <t>3人：刺客攻击 18% 概率造成 3.5 倍暴击
+6人：暴击伤害提升至 4.5 倍（现有成员 7 人）</t>
         </is>
       </c>
     </row>
@@ -2176,8 +2176,8 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2人：狂战吸血 15%
-4人：狂战吸血 25%（现有成员 5 人）</t>
+          <t>2人：狂战吸血 26%
+4人：狂战吸血 42%（现有成员 5 人）</t>
         </is>
       </c>
     </row>
@@ -2194,8 +2194,8 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2人：全队每秒回复 2 生命
-4人：全队每秒回复 4 生命（现有成员 4 人）</t>
+          <t>2人：全队每秒回复 1 生命
+4人：全队每秒回复 2 生命（现有成员 4 人）</t>
         </is>
       </c>
     </row>
@@ -2212,8 +2212,8 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2人：全队攻击 +8%
-3人：全队攻击 +16%（现有成员 3 人）</t>
+          <t>2人：全队攻击 +1%
+3人：全队攻击 +2%（现有成员 3 人）</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t>2人：星际棋子开局蓝量拉满
-3人：星际棋子开局蓝量拉满，技能伤害 +25%（现有成员 3 人）</t>
+3人：星际棋子开局蓝量拉满，技能伤害 +12%（现有成员 3 人）</t>
         </is>
       </c>
     </row>
@@ -2332,8 +2332,8 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2人：音律棋子攻速 +30%
-4人：音律棋子攻速 +50%（现有成员 4 人）</t>
+          <t>2人：音律棋子攻速 +22%
+4人：音律棋子攻速 +36%（现有成员 4 人）</t>
         </is>
       </c>
     </row>
@@ -2350,8 +2350,8 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2人：四禧丸子棋子生命 +15%
-4人：四禧丸子棋子生命 +30%（现有成员 4 人）</t>
+          <t>2人：四禧丸子棋子生命 +18%
+4人：四禧丸子棋子生命 +36%（现有成员 4 人）</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2人：花语棋子生命 +20%（现有成员 3 人）</t>
+          <t>2人：花语棋子生命 +10%（现有成员 3 人）</t>
         </is>
       </c>
     </row>
@@ -2420,8 +2420,8 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2人：魔道棋子被近战攻击时 20% 概率石化攻击者 1.5 秒
-4人：概率提升至 35%（现有成员 4 人）</t>
+          <t>2人：魔道棋子被近战攻击时 40% 概率石化攻击者 1.5 秒
+4人：概率提升至 64%（现有成员 4 人）</t>
         </is>
       </c>
     </row>
@@ -2456,8 +2456,8 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2人：随机一名友军获得 8 护甲并每秒回复 3 生命
-4人：随机两名友军获得 12 护甲并每秒回复 5 生命（现有成员 4 人）</t>
+          <t>2人：随机一名友军获得 10 护甲并每秒回复 4 生命
+4人：随机两名友军获得 16 护甲并每秒回复 7 生命（现有成员 4 人）</t>
         </is>
       </c>
     </row>
@@ -2474,8 +2474,8 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2人：P-SP 棋子攻击 20% 概率沉默目标 3 秒
-4人：概率提升至 40%（现有成员 8 人）</t>
+          <t>2人：P-SP 棋子攻击 10% 概率沉默目标 3 秒
+4人：概率提升至 24%（现有成员 8 人）</t>
         </is>
       </c>
     </row>

--- a/虚拟棋战_棋子与羁绊_20260914.xlsx
+++ b/虚拟棋战_棋子与羁绊_20260914.xlsx
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>紫藤突刺：瞬步到最远的敌人身边，对其造成 214% 攻击伤害，突进至最远的敌人，并永久获得 15% 吸血</t>
+          <t>紫藤突刺：瞬步到最远的敌人身边，对其造成 214% 攻击伤害，突进至最远的敌人，并永久获得 15% 吸血（专属暴击 20%/2.2×）</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>熊猫跃袭：瞬步到最远的敌人身边，对其造成 246% 攻击伤害，突进至最远的敌人；目标生命低于 35% 时追加 60% 斩杀伤害</t>
+          <t>熊猫跃袭：瞬步到最远的敌人身边，对其造成 246% 攻击伤害，突进至最远的敌人；目标生命低于 35% 时追加 60% 斩杀伤害（专属暴击 20%/2.5×）</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>月影斩：瞬步到最远的敌人身边，对其造成 282% 攻击伤害，并附加每 3 秒 2% 最大生命的毒伤</t>
+          <t>月影斩：瞬步到最远的敌人身边，对其造成 282% 攻击伤害，并附加每 3 秒 2% 最大生命的毒伤（专属暴击 15%/2.2×）</t>
         </is>
       </c>
     </row>
